--- a/codigos/Codigos_resNet/Letras intrasf/Resumen.xlsx
+++ b/codigos/Codigos_resNet/Letras intrasf/Resumen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\VJaroszewski-econ\codigos\Codigos_resNet\Letras intrasf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{41851E8F-17D5-4A9F-91AC-8DF886017E92}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{587B2721-2A38-4D8D-AB91-54935582240F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{4EEAC442-6966-40E0-A4D6-EA152B6F33B4}"/>
+    <workbookView xWindow="375" yWindow="975" windowWidth="20460" windowHeight="10890" xr2:uid="{4EEAC442-6966-40E0-A4D6-EA152B6F33B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -267,12 +267,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -292,6 +286,12 @@
     <xf numFmtId="44" fontId="0" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -900,555 +900,596 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="2" t="s">
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
       <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="4" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+      <c r="A3" s="2">
         <f>+[1]Sheet1!A9</f>
         <v>45747</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="3">
         <f>+[1]Sheet1!C9/1000</f>
         <v>24986.32932976371</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="3">
         <f>+[1]Sheet1!D9/1000</f>
         <v>23560.539473402401</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="6">
         <f>+[1]Sheet1!$F9/1000</f>
         <v>114389.81810452799</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="3">
         <f>+[1]Sheet1!$H9/1000</f>
         <v>7149.7774321964853</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="3">
         <f>+[1]Sheet1!$J9/1000</f>
         <v>20678.111356535912</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="3">
         <f>+[1]Sheet1!$K9/1000</f>
         <v>86934.811976254219</v>
       </c>
-      <c r="H3" s="5">
-        <f>+G3+D3</f>
-        <v>201324.63008078223</v>
+      <c r="H3" s="3">
+        <f>+D3-G3</f>
+        <v>27455.006128273773</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+      <c r="A4" s="2">
         <f>+[1]Sheet1!$A10</f>
         <v>45754</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="5">
         <f>+[1]Sheet1!$C10/1000</f>
         <v>24837.944542828882</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="3">
         <f>+[1]Sheet1!D10/1000</f>
         <v>23622.483419401779</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="6">
         <f>+[1]Sheet1!$F10/1000</f>
         <v>117583.5146018431</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="5">
         <f>+[1]Sheet1!$H10/1000</f>
         <v>7094.7791060631498</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="3">
         <f>+[1]Sheet1!$J10/1000</f>
         <v>20397.747404080132</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="3">
         <f>+[1]Sheet1!$K10/1000</f>
         <v>90565.621040434227</v>
       </c>
-      <c r="H4" s="5">
-        <f>+G4+D4</f>
-        <v>208149.13564227731</v>
-      </c>
-      <c r="I4" s="18"/>
+      <c r="H4" s="3">
+        <f t="shared" ref="H4:H9" si="0">+D4-G4</f>
+        <v>27017.89356140887</v>
+      </c>
+      <c r="I4" s="16"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
+      <c r="A5" s="2">
         <f>+[1]Sheet1!$A11</f>
         <v>45762</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="5">
         <f>+[1]Sheet1!$C11/1000</f>
         <v>36776.802006573271</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="3">
         <f>+[1]Sheet1!D11/1000</f>
         <v>23713.298183852829</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="6">
         <f>+[1]Sheet1!$F11/1000</f>
         <v>127216.0105886471</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="5">
         <f>+[1]Sheet1!$H11/1000</f>
         <v>18670.188630678382</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="3">
         <f>+[1]Sheet1!$J11/1000</f>
         <v>20480.9726778896</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="3">
         <f>+[1]Sheet1!$K11/1000</f>
         <v>99645.272438730666</v>
       </c>
-      <c r="H5" s="5">
-        <f>+G5+D5</f>
-        <v>226861.28302737777</v>
-      </c>
-      <c r="I5" s="18"/>
+      <c r="H5" s="3">
+        <f t="shared" si="0"/>
+        <v>27570.738149916433</v>
+      </c>
+      <c r="I5" s="16"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
+      <c r="A6" s="2">
         <f>+[1]Sheet1!$A12</f>
         <v>45770</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="3">
         <f>+[1]Sheet1!$C12/1000</f>
         <v>38630.696261915371</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="3">
         <f>+[1]Sheet1!D12/1000</f>
         <v>23778.732500668149</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="6">
         <f>+[1]Sheet1!$F12/1000</f>
         <v>128471.03066636971</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="3">
         <f>+[1]Sheet1!$H12/1000</f>
         <v>18989.259219599109</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="5">
         <f>+[1]Sheet1!$J12/1000</f>
         <v>31035.17846948775</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="3">
         <f>+[1]Sheet1!$K12/1000</f>
         <v>109742.6170387528</v>
       </c>
-      <c r="H6" s="5">
-        <f>+G6+D6</f>
-        <v>238213.64770512251</v>
-      </c>
-      <c r="I6" s="18"/>
+      <c r="H6" s="3">
+        <f t="shared" si="0"/>
+        <v>18728.413627616916</v>
+      </c>
+      <c r="I6" s="16"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
+      <c r="A7" s="2">
         <f>+[1]Sheet1!$A13</f>
         <v>45777</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="3">
         <f>+[1]Sheet1!$C13/1000</f>
         <v>38928.249987201365</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="5">
         <f>+[1]Sheet1!D13/1000</f>
         <v>23851.8416552901</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="6">
         <f>+[1]Sheet1!$F13/1000</f>
         <v>125912.14034300341</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="5">
         <f>+[1]Sheet1!$H13/1000</f>
         <v>27135.114191126278</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="5">
         <f>+[1]Sheet1!$J13/1000</f>
         <v>20427.858763651882</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="3">
         <f>+[1]Sheet1!$K13/1000</f>
         <v>107675.4927397611</v>
       </c>
-      <c r="H7" s="5">
-        <f>+G7+D7</f>
-        <v>233587.63308276451</v>
-      </c>
-      <c r="I7" s="18"/>
+      <c r="H7" s="3">
+        <f t="shared" si="0"/>
+        <v>18236.647603242309</v>
+      </c>
+      <c r="I7" s="16"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
+      <c r="A8" s="2">
         <f>+[1]Sheet1!$A14</f>
         <v>45784</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="3">
         <f>+[1]Sheet1!$C14/1000</f>
         <v>38258.33100216731</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="5">
         <f>+[1]Sheet1!D14/1000</f>
         <v>16092.30106371912</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="6">
         <f>+[1]Sheet1!$F14/1000</f>
         <v>122440.2881586476</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="5">
         <f>+[1]Sheet1!$H14/1000</f>
         <v>14628.23704638058</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="3">
         <f>+[1]Sheet1!$J14/1000</f>
         <v>20646.282784568702</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="3">
         <f>+[1]Sheet1!$K14/1000</f>
         <v>99261.180099696576</v>
       </c>
-      <c r="H8" s="5">
-        <f>+G8+D8</f>
-        <v>221701.46825834416</v>
-      </c>
-      <c r="I8" s="18"/>
+      <c r="H8" s="3">
+        <f t="shared" si="0"/>
+        <v>23179.108058951024</v>
+      </c>
+      <c r="I8" s="16"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
+      <c r="A9" s="2">
         <f>+[1]Sheet1!$A15</f>
         <v>45792</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="3">
         <f>+[1]Sheet1!$C15/1000</f>
         <v>38346.281282254517</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="3">
         <f>+[1]Sheet1!D15/1000</f>
         <v>16160.49900396301</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="6">
         <f>+[1]Sheet1!$F15/1000</f>
         <v>120767.77686129459</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="3">
         <f>+[1]Sheet1!$H15/1000</f>
         <v>13797.360444738</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="3">
         <f>+[1]Sheet1!$J15/1000</f>
         <v>20919.07788199031</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="3">
         <f>+[1]Sheet1!$K15/1000</f>
         <v>96586.562569793052</v>
       </c>
-      <c r="H9" s="5">
-        <f>+G9+D9</f>
-        <v>217354.33943108766</v>
-      </c>
-      <c r="I9" s="18"/>
+      <c r="H9" s="3">
+        <f t="shared" si="0"/>
+        <v>24181.214291501543</v>
+      </c>
+      <c r="I9" s="16"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="F11" s="5"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="F11" s="3"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="22">
+      <c r="A12" s="20">
         <v>46123</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="20">
         <v>46127</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
       </c>
-      <c r="K12" s="11"/>
+      <c r="K12" s="9"/>
     </row>
     <row r="13" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="10"/>
+      <c r="B13" s="8"/>
       <c r="F13" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="11">
         <f>+E5-E4</f>
         <v>11575.409524615232</v>
       </c>
-      <c r="D14" s="9"/>
+      <c r="D14" s="7"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13">
         <f>+B5-B4</f>
         <v>11938.857463744389</v>
       </c>
-      <c r="F15" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" s="13">
+      <c r="E15" s="3">
         <f>+E7-E6</f>
         <v>8145.8549715271693</v>
       </c>
+      <c r="F15" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="11">
+        <f>+E7-E6</f>
+        <v>8145.8549715271693</v>
+      </c>
     </row>
     <row r="16" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="17">
+      <c r="C16" s="15">
         <f>C8-C7</f>
         <v>-7759.5405915709798</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="E16" s="3"/>
+      <c r="F16" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="17">
+      <c r="G16" s="15">
         <f>+E8-E4</f>
         <v>7533.4579403174303</v>
       </c>
     </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C17" s="3">
+        <f>+E8-E7</f>
+        <v>-12506.877144745698</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3">
+        <f>3500+12100</f>
+        <v>15600</v>
+      </c>
+    </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D18" s="21"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="3">
+        <f>+E17+E4</f>
+        <v>22694.77910606315</v>
+      </c>
+      <c r="F18" s="3"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C19" s="3">
+        <f>+B6-B5</f>
+        <v>1853.8942553421002</v>
+      </c>
+      <c r="E19" s="3">
+        <f>+E18+C16</f>
+        <v>14935.23851449217</v>
+      </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
+      <c r="E20" s="3">
+        <f>+E19+C16</f>
+        <v>7175.6979229211902</v>
+      </c>
+      <c r="F20" s="3">
+        <f>+E8-E4</f>
+        <v>7533.4579403174303</v>
+      </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="F21" s="3">
+        <f>+F20-C16</f>
+        <v>15292.99853188841</v>
+      </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="2" t="s">
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
       <c r="H22" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="G23" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="H23" s="4" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="4">
+      <c r="A24" s="2">
         <f>+[1]Sheet1!$A25</f>
         <v>45869</v>
       </c>
-      <c r="B24" s="20">
+      <c r="B24" s="18">
         <f>+[1]Sheet1!$C25/1000</f>
         <v>38865.967038243551</v>
       </c>
-      <c r="C24" s="10">
+      <c r="C24" s="8">
         <f>+[1]Sheet1!$D25/1000</f>
         <v>16821.120790559009</v>
       </c>
-      <c r="D24" s="10">
+      <c r="D24" s="8">
         <f>+[1]Sheet1!$F25/1000</f>
         <v>125726.3900696928</v>
       </c>
-      <c r="E24" s="20">
+      <c r="E24" s="18">
         <f>+[1]Sheet1!$H25/1000</f>
         <v>13239.472300319869</v>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="8">
         <f>+[1]Sheet1!$J25/1000</f>
         <v>22354.217314368569</v>
       </c>
-      <c r="G24" s="10">
+      <c r="G24" s="8">
         <f>+[1]Sheet1!$K25/1000</f>
         <v>102981.0824137858</v>
       </c>
-      <c r="H24" s="10">
+      <c r="H24" s="8">
         <f>+[1]Sheet1!$L25/1000</f>
         <v>22745.307655906978</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="4">
+      <c r="A25" s="2">
         <f>+[1]Sheet1!$A26</f>
         <v>45876</v>
       </c>
-      <c r="B25" s="20">
+      <c r="B25" s="18">
         <f>+[1]Sheet1!$C26/1000</f>
         <v>41682.91594147413</v>
       </c>
-      <c r="C25" s="20">
+      <c r="C25" s="18">
         <f>+[1]Sheet1!$D26/1000</f>
         <v>16880.683266779768</v>
       </c>
-      <c r="D25" s="10">
+      <c r="D25" s="8">
         <f>+[1]Sheet1!$F26/1000</f>
         <v>130214.3098625007</v>
       </c>
-      <c r="E25" s="20">
+      <c r="E25" s="18">
         <f>+[1]Sheet1!$H26/1000</f>
         <v>14732.15963043034</v>
       </c>
-      <c r="F25" s="10">
+      <c r="F25" s="8">
         <f>+[1]Sheet1!$J26/1000</f>
         <v>22121.047675228143</v>
       </c>
-      <c r="G25" s="10">
+      <c r="G25" s="8">
         <f>+[1]Sheet1!$K26/1000</f>
         <v>106788.0860228657</v>
       </c>
-      <c r="H25" s="10">
+      <c r="H25" s="8">
         <f>+[1]Sheet1!$L26/1000</f>
         <v>23426.223839634982</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="4">
+      <c r="A26" s="2">
         <f>+[1]Sheet1!$A27</f>
         <v>45884</v>
       </c>
-      <c r="B26" s="10">
+      <c r="B26" s="8">
         <f>+[1]Sheet1!$C27/1000</f>
         <v>41907.553714332578</v>
       </c>
-      <c r="C26" s="20">
+      <c r="C26" s="18">
         <f>+[1]Sheet1!$D27/1000</f>
         <v>15328.24213065585</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D26" s="8">
         <f>+[1]Sheet1!$F27/1000</f>
         <v>129342.92883548861</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E26" s="8">
         <f>+[1]Sheet1!$H27/1000</f>
         <v>12849.219334247629</v>
       </c>
-      <c r="F26" s="10">
+      <c r="F26" s="8">
         <f>+[1]Sheet1!$J27/1000</f>
         <v>22621.50795290466</v>
       </c>
-      <c r="G26" s="10">
+      <c r="G26" s="8">
         <f>+[1]Sheet1!$K27/1000</f>
         <v>105846.24616449029</v>
       </c>
-      <c r="H26" s="10">
+      <c r="H26" s="8">
         <f>+[1]Sheet1!$L27/1000</f>
         <v>23496.682670998278</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="4">
+      <c r="A27" s="2">
         <f>+[1]Sheet1!$A28</f>
         <v>45892</v>
       </c>
-      <c r="B27" s="10">
+      <c r="B27" s="8">
         <f>+[1]Sheet1!$C28/1000</f>
         <v>41504.681015566704</v>
       </c>
-      <c r="C27" s="10">
+      <c r="C27" s="8">
         <f>+[1]Sheet1!$D28/1000</f>
         <v>15389.48643267511</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D27" s="8">
         <f>+[1]Sheet1!$F28/1000</f>
         <v>128516.7526102971</v>
       </c>
-      <c r="E27" s="10">
+      <c r="E27" s="8">
         <f>+[1]Sheet1!$H28/1000</f>
         <v>11007.417258526189</v>
       </c>
-      <c r="F27" s="10">
+      <c r="F27" s="8">
         <f>+[1]Sheet1!$J28/1000</f>
         <v>22534.91127649691</v>
       </c>
-      <c r="G27" s="10">
+      <c r="G27" s="8">
         <f>+[1]Sheet1!$K28/1000</f>
         <v>105728.75403162251</v>
       </c>
-      <c r="H27" s="10">
+      <c r="H27" s="8">
         <f>+[1]Sheet1!$L28/1000</f>
         <v>22787.998578674527</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="22">
+      <c r="A29" s="20">
         <v>46234</v>
       </c>
       <c r="B29" t="s">
@@ -1459,35 +1500,35 @@
       <c r="B30" t="s">
         <v>19</v>
       </c>
-      <c r="E30" s="5"/>
+      <c r="E30" s="3"/>
     </row>
     <row r="31" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C31" s="5"/>
+      <c r="C31" s="3"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C32" s="13">
+      <c r="C32" s="11">
         <f>+E24-E25</f>
         <v>-1492.6873301104715</v>
       </c>
-      <c r="E32" s="5"/>
+      <c r="E32" s="3"/>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="14" t="s">
+      <c r="B33" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C33" s="15">
+      <c r="C33" s="13">
         <f>+B25-B24</f>
         <v>2816.9489032305792</v>
       </c>
     </row>
     <row r="34" spans="2:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="16" t="s">
+      <c r="B34" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C34" s="17">
+      <c r="C34" s="15">
         <f>+C26-C25</f>
         <v>-1552.4411361239181</v>
       </c>
